--- a/important_mails_2026-07-20.xlsx
+++ b/important_mails_2026-07-20.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H225"/>
+  <dimension ref="A1:H218"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3537,7 +3537,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>店铺绩效类</t>
+          <t>KYC审核类</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -3552,179 +3552,21 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Sat, 20 Jun 2026 15:35:08 +0000</t>
+          <t>Mon, 13 Jul 2026 06:09:58 +0000</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
+          <t>亚马逊全球开店 &lt;info@globalselling.amazon.cn&gt;</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>Your FBA request is complete (hCxOB8pPpU)</t>
+          <t>【官方提示】请尽快通过您的欧洲站卖家资质KYC审核，以保证正常销售</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr"/>
       <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>Greetings from Amazon.com
-We thought you'd like to know that we have completed your destroy request.
-Disposal Summary:
-Quantity Requested: 1
-Quantity Successfully Destroyed: 1
-Quantity Cancelled: 0
-You can track the status of this request by visiting your Seller Account at:
-https://sellercentral.amazon.com/
-For a complete list of inventory being destroyed, go to:
-https://sellercentral.amazon.com/gp/orders/fba-order-details.html?orderID=S01-0438203-1064657
-Please note: this email was sent from a notification-only address that
-cannot accept incoming e-mail. Please do not reply to this message.
-Thank you for using Fulfillment by Amazon.
---------------------------------------------------------------------------
-Fulfillment by Amazon, professional packing, shipping and servicing of
-online orders.
---------------------------------------------------------------------------
-Was this email helpful?
- https://sellercentral.amazon.com/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=PRODUCT_REMOVAL_ORDER_SHIPPED_NOW
-SPC-USAmazon-439806876012022</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>店铺绩效类</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 20 Jun 2026 15:10:33 +0000</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t>Automated unfulfillable FBA inventory removal notification</t>
-        </is>
-      </c>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr">
-        <is>
-          <t>96
- Hello Weihai US,
-The following automated unfulfillable FBA removal orders have been created based on your automated settings.
- Removal order ID hbXn1jQJTV
- You can view the removals on Removal Order Details in your seller account by using the Search tool.
-The next removal order will be created as scheduled on June 21, 2026 in accordance with your settings if you have unfulfillable inventory at that time.
-To make changes to the shipping address, frequency of your automated unfulfillable removals, or other settings, go to Automated unfulfillable removal settings in your seller account.
- Thank you.
-The Fulfillment by Amazon team
-Please note: This email was sent from a notification-only address that cannot accept incoming email. Please do not reply to this email.
- Report an issue with this email
- If you have any questions visit: Seller Central
- To change your email preferences visit: Notification Preferences
- Copyright 2026 Amazon, Inc, or its affiliates. All rights reserved.
- Amazon.com, 410 Terry Avenue North, Seattle, WA 98109-5210
- SPC-USAmazon-2163841110748510</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>店铺绩效类</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 20 Jun 2026 04:41:46 +0000</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>FBA reimbursement notification</t>
-        </is>
-      </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>96
-FBA reimbursement notification
- You have a reimbursement activity
- Hello from Fulfilment by Amazon,
-We have initiated a reimbursement, a reimbursement reversal, or both due to recent activity on your selling account. No action is required from you.
-Reimbursements can be initiated for an issue that you notified us about or one that we identified at a fulfilment centre. A reimbursement reversal occurs when a reimbursement decision has been reviewed and changed. Reimbursement amounts are determined in accordance with the FBA inventory reimbursement policy ( https://sellercentral.amazon.co.uk/gp/help/external/200213130 ).
-Please note that it may take up to five business days for reimbursement transactions to appear in your seller account.
-You can find details on your reimbursement or reversal transaction in the Reimbursements report ( https://sellercentral.amazon.co.uk/reportcentral/REIMBURSEMENTS/0 ) in Seller Central:
-- In the Event Date drop-down menu, select a date range and click Generate report . You can use the date in the subject line of this email as a point of reference.
-- To identify inventory reimbursements and reversals, see the Quantity reimbursed [inventory] column.
--</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>KYC审核类</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
-        <is>
-          <t>Mon, 13 Jul 2026 06:09:58 +0000</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="inlineStr">
-        <is>
-          <t>亚马逊全球开店 &lt;info@globalselling.amazon.cn&gt;</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="inlineStr">
-        <is>
-          <t>【官方提示】请尽快通过您的欧洲站卖家资质KYC审核，以保证正常销售</t>
-        </is>
-      </c>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">账户注册
 															资质审查
@@ -3757,39 +3599,39 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>KYC审核类</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Sat, 11 Jul 2026 08:27:01 +0000</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central Notifications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>Know Your Customer (KYC) verification process support</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>96
  Pending Know Your Customer (KYC) account verification
@@ -3806,40 +3648,40 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>KYC审核类</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Sat, 11 Jul 2026 08:25:53 +0000</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>"seller-verification-review-cn@amazon.co.uk" &lt;seller-verification-review-cn@amazon.co.uk&gt;</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>[Action Required] Information needed for your Selling on Amazon
  payment account</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>96
 [Action Required] Information needed for your Selling on Amazon payment account
@@ -3854,39 +3696,39 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>KYC审核类</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Jul 2026 11:11:12 +0000</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central Notifications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>Know Your Customer (KYC) verification process support</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>96
  Pending Know Your Customer (KYC) account verification
@@ -3903,39 +3745,39 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Mon, 13 Jul 2026 14:21:36 +0000</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3955,39 +3797,39 @@
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Mon, 13 Jul 2026 04:03:58 +0000</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4004,39 +3846,39 @@
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Sat, 11 Jul 2026 10:36:54 +0000</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4053,39 +3895,39 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Sat, 11 Jul 2026 10:30:59 +0000</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4105,39 +3947,39 @@
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Jul 2026 23:31:39 +0000</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4157,39 +3999,39 @@
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Jul 2026 12:07:00 +0000</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>完成账户验证以恢复付款</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>96
  完成账户验证以恢复付款
@@ -4232,39 +4074,39 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Jul 2026 12:05:39 +0000</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>Completa la verificación de la cuenta para restaurar los pagos</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>96
  Completa la verificación de la cuenta para restaurar los pagos
@@ -4281,39 +4123,39 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Jul 2026 12:04:08 +0000</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>Accountverificatie voltooien om vergoedingen te herstellen</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>96
  Accountverificatie voltooien om vergoedingen te herstellen
@@ -4330,39 +4172,39 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Jul 2026 12:02:02 +0000</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>Complete account verification to restore disbursements</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>96
  Complete account verification to restore disbursements
@@ -4380,39 +4222,39 @@
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Jul 2026 12:00:06 +0000</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>Ukończ weryfikację konta, aby przywrócić wypłaty środków</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>96
  Ukończ weryfikację konta, aby przywrócić wypłaty środków
@@ -4429,39 +4271,39 @@
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Jul 2026 11:59:04 +0000</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>Slutför kontoverifieringen så att utbetalningarna kan återställas</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>96
  Slutför kontoverifieringen så att utbetalningarna kan återställas
@@ -4478,39 +4320,39 @@
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Jul 2026 11:57:07 +0000</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>Completa la verifica dell'account per ripristinare i pagamenti</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>96
  Completa la verifica dell'account per ripristinare i pagamenti
@@ -4527,39 +4369,39 @@
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Jul 2026 11:55:07 +0000</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>Complete account verification to restore disbursements</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>96
  Complete account verification to restore disbursements
@@ -4577,39 +4419,39 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Jul 2026 11:53:42 +0000</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>Terminez la vérification du compte pour restaurer les versements.</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>96
  Terminez la vérification du compte pour restaurer les versements.
@@ -4626,39 +4468,39 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Jul 2026 11:44:42 +0000</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>完成账户验证以恢复付款</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr"/>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>96
  完成账户验证以恢复付款
@@ -4701,39 +4543,39 @@
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Jul 2026 15:12:23 +0000</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.pl&gt;</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>Nieuregulowane saldo na koncie Amazon</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr"/>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>Witamy!
  Masz na swoim koncie nieuregulowane saldo w wysokośc PLN 13.18. Obciążymy tą kwotą kartę kredytową zarejestrowaną jako metoda płatności dla Twojego konta
@@ -4747,39 +4589,39 @@
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Jul 2026 14:31:14 +0000</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr"/>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4796,39 +4638,39 @@
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Jul 2026 14:31:07 +0000</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr"/>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4848,39 +4690,39 @@
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Jul 2026 13:15:46 +0000</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr"/>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4897,39 +4739,39 @@
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Jul 2026 12:15:55 +0000</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>Get your Ireland VAT registration covered – €1,250 paid by Amazon</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Activate placement in Ireland and Amazon covers your VAT registration and filing costs.
@@ -4950,39 +4792,39 @@
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Jul 2026 05:23:29 +0000</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4999,39 +4841,39 @@
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Sun, 5 Jul 2026 13:51:10 +0000</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5048,39 +4890,39 @@
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Fri, 3 Jul 2026 14:39:15 +0000</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr"/>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5097,39 +4939,39 @@
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Fri, 3 Jul 2026 10:10:03 +0000</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>✅ Transparency Payment Confirmed!</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr"/>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>96
  Hello,
@@ -5153,39 +4995,39 @@
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Jul 2026 17:09:13 +0000</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>Access your January–March 2026 China tax report</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr"/>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>96
  You can now download your quarterly tax report, which includes data such as identity information, number of transactions, revenue, and commission and service fees.
@@ -5201,39 +5043,39 @@
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Jul 2026 16:54:53 +0000</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>Access your January - March 2026 China tax report</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>96
  You can now download your quarterly tax report which includes data such as identity information, number of transactions, revenue, and commission and service fees.
@@ -5249,39 +5091,39 @@
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Jul 2026 14:45:45 +0000</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr"/>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5301,39 +5143,39 @@
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Jul 2026 14:43:29 +0000</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr"/>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5350,39 +5192,39 @@
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Jul 2026 14:42:06 +0000</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr"/>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5402,39 +5244,39 @@
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Mon, 29 Jun 2026 14:21:30 +0000</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5454,39 +5296,39 @@
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Mon, 29 Jun 2026 14:17:27 +0000</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr"/>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5503,39 +5345,39 @@
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Sun, 28 Jun 2026 03:31:27 +0000</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr"/>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5555,39 +5397,39 @@
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Sun, 28 Jun 2026 03:28:55 +0000</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr"/>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5607,39 +5449,39 @@
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Fri, 26 Jun 2026 14:38:10 +0000</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr"/>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5656,39 +5498,39 @@
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Fri, 26 Jun 2026 14:37:54 +0000</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr"/>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5708,39 +5550,39 @@
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Thu, 25 Jun 2026 13:52:57 +0000</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr"/>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5757,39 +5599,39 @@
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>Thu, 25 Jun 2026 13:51:45 +0000</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr"/>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5809,39 +5651,39 @@
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>Thu, 25 Jun 2026 13:45:52 +0000</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr"/>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5861,39 +5703,39 @@
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>Thu, 25 Jun 2026 01:48:12 +0000</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>Updated China tax report link for October - December 2025</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr"/>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>96
  We’re resending your quarterly tax report which includes data such as identity information, number of transactions, revenue, and commission and service fees.
@@ -5911,39 +5753,39 @@
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>Tue, 23 Jun 2026 16:59:05 +0000</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>Download your China tax report for October - December 2025</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr"/>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>96
  You can now download your quarterly tax report which includes data such as identity information, number of transactions, revenue, and commission and service fees.
@@ -5959,39 +5801,39 @@
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>Tue, 23 Jun 2026 14:09:38 +0000</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr"/>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6011,39 +5853,39 @@
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>Tue, 23 Jun 2026 14:09:19 +0000</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr"/>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6060,39 +5902,39 @@
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Mon, 22 Jun 2026 16:37:09 +0000</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;informacion-vendedor@amazon.mx&gt;</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>Pago del saldo en tu cuenta de pagos de Vender en Amazon</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr"/>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>Estimado vendedor:
  Hemos realizado un cargo en tu tarjeta de crédito (Visa) por valor de MXN 192.85 con el fin de saldar tu cuenta de vendedor de Amazon.
@@ -6104,39 +5946,39 @@
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>Mon, 22 Jun 2026 14:05:42 +0000</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr"/>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6156,39 +5998,39 @@
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Mon, 22 Jun 2026 12:44:57 +0000</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr"/>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6205,39 +6047,39 @@
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>Sun, 21 Jun 2026 12:50:33 +0000</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr"/>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6257,89 +6099,40 @@
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 20 Jun 2026 13:23:55 +0000</t>
-        </is>
-      </c>
-      <c r="E115" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F115" s="2" t="inlineStr">
-        <is>
-          <t>Tu pago está en camino</t>
-        </is>
-      </c>
-      <c r="G115" s="2" t="inlineStr"/>
-      <c r="H115" s="2" t="inlineStr">
-        <is>
-          <t>96
-This title will display on mobile devices
- ¡Enhorabuena! El pago está de camino y llegará pronto.
- El pago está en camino
-Enhorabuena, Weihai EU. Tu pago está en camino y te llegará en un plazo de tres a cinco días.
-El 06/20/26 13:23 WEST, iniciamos una transferencia a tu método de pago (cuenta bancaria terminado en 229) por un importe de €
- 216,97.
- Si el importe es inferior a lo esperado, ten en cuenta las siguientes preguntas:
- ¿Tienes saldo no disponible en tu cuenta de vendedor? Puede que hayamos reservado algo de dinero para posibles devoluciones, reclamaciones o reversiones de cargo de clientes. En este caso, el saldo de cierre de tu informe de pagos te mostrará el saldo no disponible en reserva.
- ¿Cubren tus ventas las tarifas de Amazon y las devoluciones del periodo de liquidación? El importe del pago refleja las ventas que has hecho y las tarifas de venta aplicadas tanto a dichas ventas como a cualquier promoción o servicio que hayas utilizado. Te recomendamos que revises tu informe de pagos en "Informes" de Seller Central para conocer el saldo de cierre.
-Para más información sobre los informes de pagos en Seller Central, visita nuestro curso oficial.
-Te deseamos un éx</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Jul 2026 15:01:39 +0000</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>Manage VAT &amp; EPR Requirements Directly Within Your Pan-European FBA
  Inventory Portal</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr"/>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>Visit the Pan-EU Portal to Manage Listings,﻿ Compliance &amp;amp; Expansion in EU
                                                     ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­
@@ -6347,39 +6140,39 @@
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Jul 2026 17:38:33 +0000</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>Reactivate your EU listings - GPSR compliance required</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr"/>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Reactivate your EU listings - GPSR compliance required
@@ -6399,39 +6192,39 @@
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Jul 2026 16:17:59 +0000</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>Reactivate your EU listings - GPSR compliance required</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr"/>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Reactivate your EU listings - GPSR compliance required
@@ -6451,39 +6244,39 @@
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Jul 2026 05:08:36 +0000</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr"/>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -6502,40 +6295,40 @@
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 13:22:39 +0000</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>Sell with Amazon &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>Get answers from the people who build the tools you use every day.
  Save $100</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr"/>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/-ld-EM/7z49s9x/6752554013/h/2aeQsjjzcdEfNdbvcpArxhFF9Du4sBW3WI4zsTSQPBE)
 [Speakers at Accelerate](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z4bmtj/6752554013/h/2aeQsjjzcdEfNdbvcpArxhFF9Du4sBW3WI4zsTSQPBE)
@@ -6552,39 +6345,39 @@
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 13:08:44 +0000</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr"/>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -6603,40 +6396,40 @@
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 08:00:54 +0000</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Support &lt;merch.service05@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20858098381] US - Food and Product Safety - ASIN:
  B0DD7R3PPG</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr"/>
-      <c r="H122" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 20858098381] US - Food and Product Safety - ASIN: B0DD7R3PPG
@@ -6651,40 +6444,40 @@
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 05:35:29 +0000</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Support &lt;merch.service05@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20858098381] US - Food and Product Safety - ASIN:
  B0DD7R3PPG</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr"/>
-      <c r="H123" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 20858098381] US - Food and Product Safety - ASIN: B0DD7R3PPG
@@ -6709,40 +6502,40 @@
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>Fri, 3 Jul 2026 06:41:28 +0000</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Support &lt;merch.service05@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20858098381] US - Food and Product Safety - ASIN:
  B0DD7R3PPG</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr"/>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 20858098381] US - Food and Product Safety - ASIN: B0DD7R3PPG
@@ -6757,39 +6550,39 @@
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Jul 2026 14:09:44 +0000</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>Seller Assistant is now live in France, Italy &amp; Spain</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr"/>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  AI-powered assistance is now available in Seller Central to help you manage your business more efficiently.
@@ -6807,40 +6600,40 @@
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Jul 2026 13:15:52 +0000</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>Sell with Amazon &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>The Amazon Accelerate 2026 speaker lineup is here! Register now to
  save $100</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr"/>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">[Amazon logo](https://go.amazonsellerservices.com/e/229492/-ld-EM/7z49sbm/6744236849/h/wes7VJdAGIYNS4DfvXPWWwdvIH7_mIadF_Oxp_jSZW8)
 [Speakers at Accelerate](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z49sbq/6744236849/h/wes7VJdAGIYNS4DfvXPWWwdvIH7_mIadF_Oxp_jSZW8)
@@ -6857,40 +6650,40 @@
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>Tue, 30 Jun 2026 04:09:19 +0000</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>"seller.service05@amazon.com" &lt;seller.service05@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>[Case ID 20858098381] *UPDATE* US - Food and Product Safety - ASIN:
  B0DD7R3PPG</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr"/>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>96
 [Case ID 20858098381] *UPDATE* US - Food and Product Safety - ASIN: B0DD7R3PPG
@@ -6902,40 +6695,40 @@
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>Wed, 24 Jun 2026 04:08:32 +0000</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>"seller.service05@amazon.com" &lt;seller.service05@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>[Case ID 20858098381] *UPDATE* US - Food and Product Safety - ASIN:
  B0DD7R3PPG</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr"/>
-      <c r="H128" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>96
 [Case ID 20858098381] *UPDATE* US - Food and Product Safety - ASIN: B0DD7R3PPG
@@ -6947,40 +6740,40 @@
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>Tue, 23 Jun 2026 02:52:15 +0000</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr"/>
-      <c r="H129" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC - DOC REVIEW
@@ -6999,39 +6792,39 @@
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>Sun, 12 Jul 2026 17:10:46 +0000</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr"/>
-      <c r="H130" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -7047,40 +6840,40 @@
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Jul 2026 22:17:55 +0000</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ca Fulfillment by Amazon Merchant Credit Note for
  6/2026</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr"/>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ca Fulfillment by Amazon Merchant Credit Note for 6/2026
  96
@@ -7102,39 +6895,39 @@
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Jul 2026 15:24:05 +0000</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ca Fulfillment by Amazon Merchant Invoice for 6/2026</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr"/>
-      <c r="H132" s="2" t="inlineStr">
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Your Amazon.ca Fulfillment by Amazon Merchant Invoice for 6/2026
  96
@@ -7156,39 +6949,39 @@
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Jul 2026 14:31:47 +0000</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="F129" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr"/>
-      <c r="H133" s="2" t="inlineStr">
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -7203,40 +6996,40 @@
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Jul 2026 23:30:27 +0000</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F134" s="2" t="inlineStr">
+      <c r="F130" s="2" t="inlineStr">
         <is>
           <t>Reactiva tus listings en la UE: se requiere el cumplimiento del
  Reglamento relativo a la seguridad general de los productos</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr"/>
-      <c r="H134" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr">
         <is>
           <t>96
  Reactiva tus listings en la UE: se requiere el cumplimiento del Reglamento relativo a la seguridad general de los productos
@@ -7254,39 +7047,39 @@
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Jul 2026 20:04:53 +0000</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>Activeer je EU-productvermeldingen opnieuw - VAPV-naleving vereist</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr"/>
-      <c r="H135" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Activeer je EU-productvermeldingen opnieuw - VAPV-naleving vereist
@@ -7305,39 +7098,39 @@
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Jul 2026 15:47:06 +0000</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr">
+      <c r="F132" s="2" t="inlineStr">
         <is>
           <t>Umożliw ponowną aktywację ofert w UE – wymagana zgodność z rozporządzeniem w sprawie ogólnego bezpieczeństwa produktów</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr"/>
-      <c r="H136" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="inlineStr">
         <is>
           <t>96
  Umożliw ponowną aktywację ofert w UE – wymagana zgodność z rozporządzeniem w sprawie ogólnego bezpieczeństwa produktów
@@ -7355,39 +7148,39 @@
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Jul 2026 14:10:23 +0000</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F137" s="2" t="inlineStr">
+      <c r="F133" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr"/>
-      <c r="H137" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr"/>
+      <c r="H133" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Luana Camargo, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -7405,39 +7198,39 @@
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Jul 2026 12:46:14 +0000</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F138" s="2" t="inlineStr">
+      <c r="F134" s="2" t="inlineStr">
         <is>
           <t>Återaktivera dina EU-produktposter – GPSR-efterlevnad krävs</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr"/>
-      <c r="H138" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr"/>
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t>96
  Återaktivera dina EU-produktposter – GPSR-efterlevnad krävs
@@ -7456,39 +7249,39 @@
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Jul 2026 10:28:11 +0000</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F139" s="2" t="inlineStr">
+      <c r="F135" s="2" t="inlineStr">
         <is>
           <t>Riattivare le offerte nell'UE - Richiesta la conformità al Regolamento sulla sicurezza generale dei prodotti</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr"/>
-      <c r="H139" s="2" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr"/>
+      <c r="H135" s="2" t="inlineStr">
         <is>
           <t>96
  Riattivare le offerte nell'UE - Richiesta la conformità al Regolamento sulla sicurezza generale dei prodotti
@@ -7507,39 +7300,39 @@
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Jul 2026 09:08:55 +0000</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F140" s="2" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>Réactivez vos mises en vente dans l’UE – Conformité au RSGP requise</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr"/>
-      <c r="H140" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr"/>
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <t>96
  Réactivez vos mises en vente dans l’UE – Conformité au RSGP requise
@@ -7558,39 +7351,39 @@
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Jul 2026 08:53:55 +0000</t>
         </is>
       </c>
-      <c r="E141" s="2" t="inlineStr">
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>亚马逊卖家平台通知 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F141" s="2" t="inlineStr">
+      <c r="F137" s="2" t="inlineStr">
         <is>
           <t>解决定价错误以重新启售停售商品</t>
         </is>
       </c>
-      <c r="G141" s="2" t="inlineStr"/>
-      <c r="H141" s="2" t="inlineStr">
+      <c r="G137" s="2" t="inlineStr"/>
+      <c r="H137" s="2" t="inlineStr">
         <is>
           <t>96
  因错价而被禁止显示
@@ -7628,40 +7421,40 @@
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Jul 2026 20:45:55 +0000</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F142" s="2" t="inlineStr">
+      <c r="F138" s="2" t="inlineStr">
         <is>
           <t>Reactiva tus listings en la UE: se requiere el cumplimiento del
  Reglamento relativo a la seguridad general de los productos</t>
         </is>
       </c>
-      <c r="G142" s="2" t="inlineStr"/>
-      <c r="H142" s="2" t="inlineStr">
+      <c r="G138" s="2" t="inlineStr"/>
+      <c r="H138" s="2" t="inlineStr">
         <is>
           <t>96
  Reactiva tus listings en la UE: se requiere el cumplimiento del Reglamento relativo a la seguridad general de los productos
@@ -7679,39 +7472,39 @@
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="inlineStr">
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Jul 2026 18:16:40 +0000</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="E139" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F143" s="2" t="inlineStr">
+      <c r="F139" s="2" t="inlineStr">
         <is>
           <t>Activeer je EU-productvermeldingen opnieuw - VAPV-naleving vereist</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr"/>
-      <c r="H143" s="2" t="inlineStr">
+      <c r="G139" s="2" t="inlineStr"/>
+      <c r="H139" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Activeer je EU-productvermeldingen opnieuw - VAPV-naleving vereist
@@ -7730,39 +7523,39 @@
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Jul 2026 14:45:21 +0000</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="E140" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F144" s="2" t="inlineStr">
+      <c r="F140" s="2" t="inlineStr">
         <is>
           <t>Umożliw ponowną aktywację ofert w UE – wymagana zgodność z rozporządzeniem w sprawie ogólnego bezpieczeństwa produktów</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr"/>
-      <c r="H144" s="2" t="inlineStr">
+      <c r="G140" s="2" t="inlineStr"/>
+      <c r="H140" s="2" t="inlineStr">
         <is>
           <t>96
  Umożliw ponowną aktywację ofert w UE – wymagana zgodność z rozporządzeniem w sprawie ogólnego bezpieczeństwa produktów
@@ -7780,39 +7573,39 @@
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Jul 2026 12:00:55 +0000</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="E141" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F145" s="2" t="inlineStr">
+      <c r="F141" s="2" t="inlineStr">
         <is>
           <t>Återaktivera dina EU-produktposter – GPSR-efterlevnad krävs</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr"/>
-      <c r="H145" s="2" t="inlineStr">
+      <c r="G141" s="2" t="inlineStr"/>
+      <c r="H141" s="2" t="inlineStr">
         <is>
           <t>96
  Återaktivera dina EU-produktposter – GPSR-efterlevnad krävs
@@ -7831,39 +7624,39 @@
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Jul 2026 09:53:57 +0000</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="E142" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F146" s="2" t="inlineStr">
+      <c r="F142" s="2" t="inlineStr">
         <is>
           <t>Riattivare le offerte nell'UE - Richiesta la conformità al Regolamento sulla sicurezza generale dei prodotti</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr"/>
-      <c r="H146" s="2" t="inlineStr">
+      <c r="G142" s="2" t="inlineStr"/>
+      <c r="H142" s="2" t="inlineStr">
         <is>
           <t>96
  Riattivare le offerte nell'UE - Richiesta la conformità al Regolamento sulla sicurezza generale dei prodotti
@@ -7882,39 +7675,39 @@
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C147" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="inlineStr">
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Jul 2026 09:08:27 +0000</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F147" s="2" t="inlineStr">
+      <c r="F143" s="2" t="inlineStr">
         <is>
           <t>Réactivez vos mises en vente dans l’UE – Conformité au RSGP requise</t>
         </is>
       </c>
-      <c r="G147" s="2" t="inlineStr"/>
-      <c r="H147" s="2" t="inlineStr">
+      <c r="G143" s="2" t="inlineStr"/>
+      <c r="H143" s="2" t="inlineStr">
         <is>
           <t>96
  Réactivez vos mises en vente dans l’UE – Conformité au RSGP requise
@@ -7933,39 +7726,39 @@
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr">
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Jul 2026 05:08:12 +0000</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F148" s="2" t="inlineStr">
+      <c r="F144" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Credit Note for 6/2026</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr"/>
-      <c r="H148" s="2" t="inlineStr">
+      <c r="G144" s="2" t="inlineStr"/>
+      <c r="H144" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Credit Note for 6/2026
  96
@@ -7983,39 +7776,39 @@
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr">
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Jul 2026 04:22:50 +0000</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F149" s="2" t="inlineStr">
+      <c r="F145" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnungskorrektur Verkäufer for 6/2026</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr"/>
-      <c r="H149" s="2" t="inlineStr">
+      <c r="G145" s="2" t="inlineStr"/>
+      <c r="H145" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Your Amazon.de Rechnungskorrektur Verkäufer for 6/2026
  96
@@ -8039,39 +7832,39 @@
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Jul 2026 04:18:37 +0000</t>
         </is>
       </c>
-      <c r="E150" s="2" t="inlineStr">
+      <c r="E146" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F150" s="2" t="inlineStr">
+      <c r="F146" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Kreditnota Säljare for 6/2026</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr"/>
-      <c r="H150" s="2" t="inlineStr">
+      <c r="G146" s="2" t="inlineStr"/>
+      <c r="H146" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Kreditnota Säljare for 6/2026
  96
@@ -8098,39 +7891,39 @@
         </is>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="inlineStr">
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Jul 2026 03:58:57 +0000</t>
         </is>
       </c>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F151" s="2" t="inlineStr">
+      <c r="F147" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Logística de Amazon for 6/2026</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr"/>
-      <c r="H151" s="2" t="inlineStr">
+      <c r="G147" s="2" t="inlineStr"/>
+      <c r="H147" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Your Amazon.es Factura Logística de Amazon for 6/2026
  96
@@ -8157,39 +7950,39 @@
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="inlineStr">
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Jul 2026 03:24:51 +0000</t>
         </is>
       </c>
-      <c r="E152" s="2" t="inlineStr">
+      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F152" s="2" t="inlineStr">
+      <c r="F148" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Creditnota Fulfillment by Amazon for 6/2026</t>
         </is>
       </c>
-      <c r="G152" s="2" t="inlineStr"/>
-      <c r="H152" s="2" t="inlineStr">
+      <c r="G148" s="2" t="inlineStr"/>
+      <c r="H148" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Creditnota Fulfillment by Amazon for 6/2026
  96
@@ -8212,39 +8005,39 @@
         </is>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C153" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D153" s="2" t="inlineStr">
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Jul 2026 03:10:44 +0000</t>
         </is>
       </c>
-      <c r="E153" s="2" t="inlineStr">
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F153" s="2" t="inlineStr">
+      <c r="F149" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Creditnota Verkoper for 6/2026</t>
         </is>
       </c>
-      <c r="G153" s="2" t="inlineStr"/>
-      <c r="H153" s="2" t="inlineStr">
+      <c r="G149" s="2" t="inlineStr"/>
+      <c r="H149" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Creditnota Verkoper for 6/2026
  96
@@ -8268,39 +8061,39 @@
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="inlineStr">
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Jul 2026 03:00:23 +0000</t>
         </is>
       </c>
-      <c r="E154" s="2" t="inlineStr">
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F154" s="2" t="inlineStr">
+      <c r="F150" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Nota de Crédito Vendedor for 6/2026</t>
         </is>
       </c>
-      <c r="G154" s="2" t="inlineStr"/>
-      <c r="H154" s="2" t="inlineStr">
+      <c r="G150" s="2" t="inlineStr"/>
+      <c r="H150" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Nota de Crédito Vendedor for 6/2026
  96
@@ -8327,39 +8120,39 @@
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D155" s="2" t="inlineStr">
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Jul 2026 02:41:16 +0000</t>
         </is>
       </c>
-      <c r="E155" s="2" t="inlineStr">
+      <c r="E151" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F155" s="2" t="inlineStr">
+      <c r="F151" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Logística de Amazon for 6/2026</t>
         </is>
       </c>
-      <c r="G155" s="2" t="inlineStr"/>
-      <c r="H155" s="2" t="inlineStr">
+      <c r="G151" s="2" t="inlineStr"/>
+      <c r="H151" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Your Amazon.es Factura Logística de Amazon for 6/2026
  96
@@ -8386,39 +8179,39 @@
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="2" t="inlineStr">
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C156" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D156" s="2" t="inlineStr">
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Jul 2026 02:20:20 +0000</t>
         </is>
       </c>
-      <c r="E156" s="2" t="inlineStr">
+      <c r="E152" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F156" s="2" t="inlineStr">
+      <c r="F152" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com.be Creditnota Verkoper for 6/2026</t>
         </is>
       </c>
-      <c r="G156" s="2" t="inlineStr"/>
-      <c r="H156" s="2" t="inlineStr">
+      <c r="G152" s="2" t="inlineStr"/>
+      <c r="H152" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com.be Creditnota Verkoper for 6/2026
  96
@@ -8438,39 +8231,39 @@
         </is>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="2" t="inlineStr">
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C157" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D157" s="2" t="inlineStr">
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Jul 2026 02:05:26 +0000</t>
         </is>
       </c>
-      <c r="E157" s="2" t="inlineStr">
+      <c r="E153" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F157" s="2" t="inlineStr">
+      <c r="F153" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Creditnota Fulfillment by Amazon for 6/2026</t>
         </is>
       </c>
-      <c r="G157" s="2" t="inlineStr"/>
-      <c r="H157" s="2" t="inlineStr">
+      <c r="G153" s="2" t="inlineStr"/>
+      <c r="H153" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Creditnota Fulfillment by Amazon for 6/2026
  96
@@ -8493,39 +8286,39 @@
         </is>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" s="2" t="inlineStr">
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C158" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D158" s="2" t="inlineStr">
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Jul 2026 02:01:10 +0000</t>
         </is>
       </c>
-      <c r="E158" s="2" t="inlineStr">
+      <c r="E154" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F158" s="2" t="inlineStr">
+      <c r="F154" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 6/2026</t>
         </is>
       </c>
-      <c r="G158" s="2" t="inlineStr"/>
-      <c r="H158" s="2" t="inlineStr">
+      <c r="G154" s="2" t="inlineStr"/>
+      <c r="H154" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 6/2026
  96
@@ -8550,39 +8343,39 @@
         </is>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="2" t="inlineStr">
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C159" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D159" s="2" t="inlineStr">
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Jul 2026 00:33:27 +0000</t>
         </is>
       </c>
-      <c r="E159" s="2" t="inlineStr">
+      <c r="E155" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F159" s="2" t="inlineStr">
+      <c r="F155" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com.be Factuur Fulfilled by Amazon for 6/2026</t>
         </is>
       </c>
-      <c r="G159" s="2" t="inlineStr"/>
-      <c r="H159" s="2" t="inlineStr">
+      <c r="G155" s="2" t="inlineStr"/>
+      <c r="H155" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com.be Factuur Fulfilled by Amazon for 6/2026
  96
@@ -8601,39 +8394,39 @@
         </is>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" s="2" t="inlineStr">
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C160" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D160" s="2" t="inlineStr">
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Jul 2026 00:22:23 +0000</t>
         </is>
       </c>
-      <c r="E160" s="2" t="inlineStr">
+      <c r="E156" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F160" s="2" t="inlineStr">
+      <c r="F156" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Invoice for 6/2026</t>
         </is>
       </c>
-      <c r="G160" s="2" t="inlineStr"/>
-      <c r="H160" s="2" t="inlineStr">
+      <c r="G156" s="2" t="inlineStr"/>
+      <c r="H156" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Invoice for 6/2026
  96
@@ -8651,39 +8444,39 @@
         </is>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" s="2" t="inlineStr">
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C161" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D161" s="2" t="inlineStr">
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Jul 2026 00:13:46 +0000</t>
         </is>
       </c>
-      <c r="E161" s="2" t="inlineStr">
+      <c r="E157" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F161" s="2" t="inlineStr">
+      <c r="F157" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 6/2026</t>
         </is>
       </c>
-      <c r="G161" s="2" t="inlineStr"/>
-      <c r="H161" s="2" t="inlineStr">
+      <c r="G157" s="2" t="inlineStr"/>
+      <c r="H157" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 6/2026
  96
@@ -8708,39 +8501,39 @@
         </is>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" s="2" t="inlineStr">
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C162" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D162" s="2" t="inlineStr">
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 23:07:09 +0000</t>
         </is>
       </c>
-      <c r="E162" s="2" t="inlineStr">
+      <c r="E158" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F162" s="2" t="inlineStr">
+      <c r="F158" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com.be Factuur Fulfilled by Amazon for 6/2026</t>
         </is>
       </c>
-      <c r="G162" s="2" t="inlineStr"/>
-      <c r="H162" s="2" t="inlineStr">
+      <c r="G158" s="2" t="inlineStr"/>
+      <c r="H158" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com.be Factuur Fulfilled by Amazon for 6/2026
  96
@@ -8759,39 +8552,39 @@
         </is>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" s="2" t="inlineStr">
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C163" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D163" s="2" t="inlineStr">
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 21:44:31 +0000</t>
         </is>
       </c>
-      <c r="E163" s="2" t="inlineStr">
+      <c r="E159" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F163" s="2" t="inlineStr">
+      <c r="F159" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 6/2026</t>
         </is>
       </c>
-      <c r="G163" s="2" t="inlineStr"/>
-      <c r="H163" s="2" t="inlineStr">
+      <c r="G159" s="2" t="inlineStr"/>
+      <c r="H159" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 6/2026
  96
@@ -8816,39 +8609,39 @@
         </is>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" s="2" t="inlineStr">
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C164" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D164" s="2" t="inlineStr">
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 21:29:53 +0000</t>
         </is>
       </c>
-      <c r="E164" s="2" t="inlineStr">
+      <c r="E160" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F164" s="2" t="inlineStr">
+      <c r="F160" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Verkäufer for 6/2026</t>
         </is>
       </c>
-      <c r="G164" s="2" t="inlineStr"/>
-      <c r="H164" s="2" t="inlineStr">
+      <c r="G160" s="2" t="inlineStr"/>
+      <c r="H160" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Verkäufer for 6/2026
  96
@@ -8873,39 +8666,39 @@
         </is>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" s="2" t="inlineStr">
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C165" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D165" s="2" t="inlineStr">
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 21:23:16 +0000</t>
         </is>
       </c>
-      <c r="E165" s="2" t="inlineStr">
+      <c r="E161" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F165" s="2" t="inlineStr">
+      <c r="F161" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com.be Factuur Fulfilled by Amazon for 6/2026</t>
         </is>
       </c>
-      <c r="G165" s="2" t="inlineStr"/>
-      <c r="H165" s="2" t="inlineStr">
+      <c r="G161" s="2" t="inlineStr"/>
+      <c r="H161" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com.be Factuur Fulfilled by Amazon for 6/2026
  96
@@ -8924,39 +8717,39 @@
         </is>
       </c>
     </row>
-    <row r="166">
-      <c r="A166" s="2" t="inlineStr">
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C166" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D166" s="2" t="inlineStr">
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 21:07:51 +0000</t>
         </is>
       </c>
-      <c r="E166" s="2" t="inlineStr">
+      <c r="E162" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F166" s="2" t="inlineStr">
+      <c r="F162" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Faktura Fraktas Av Amazon for 6/2026</t>
         </is>
       </c>
-      <c r="G166" s="2" t="inlineStr"/>
-      <c r="H166" s="2" t="inlineStr">
+      <c r="G162" s="2" t="inlineStr"/>
+      <c r="H162" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Faktura Fraktas Av Amazon for 6/2026
  96
@@ -8983,39 +8776,39 @@
         </is>
       </c>
     </row>
-    <row r="167">
-      <c r="A167" s="2" t="inlineStr">
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C167" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D167" s="2" t="inlineStr">
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 20:56:46 +0000</t>
         </is>
       </c>
-      <c r="E167" s="2" t="inlineStr">
+      <c r="E163" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F167" s="2" t="inlineStr">
+      <c r="F163" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Logística de Amazon for 6/2026</t>
         </is>
       </c>
-      <c r="G167" s="2" t="inlineStr"/>
-      <c r="H167" s="2" t="inlineStr">
+      <c r="G163" s="2" t="inlineStr"/>
+      <c r="H163" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Logística de Amazon for 6/2026
  96
@@ -9042,39 +8835,39 @@
         </is>
       </c>
     </row>
-    <row r="168">
-      <c r="A168" s="2" t="inlineStr">
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C168" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D168" s="2" t="inlineStr">
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 20:36:00 +0000</t>
         </is>
       </c>
-      <c r="E168" s="2" t="inlineStr">
+      <c r="E164" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F168" s="2" t="inlineStr">
+      <c r="F164" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 6/2026</t>
         </is>
       </c>
-      <c r="G168" s="2" t="inlineStr"/>
-      <c r="H168" s="2" t="inlineStr">
+      <c r="G164" s="2" t="inlineStr"/>
+      <c r="H164" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 6/2026
  96
@@ -9099,39 +8892,39 @@
         </is>
       </c>
     </row>
-    <row r="169">
-      <c r="A169" s="2" t="inlineStr">
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C169" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D169" s="2" t="inlineStr">
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 20:27:56 +0000</t>
         </is>
       </c>
-      <c r="E169" s="2" t="inlineStr">
+      <c r="E165" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F169" s="2" t="inlineStr">
+      <c r="F165" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Vendedor for 6/2026</t>
         </is>
       </c>
-      <c r="G169" s="2" t="inlineStr"/>
-      <c r="H169" s="2" t="inlineStr">
+      <c r="G165" s="2" t="inlineStr"/>
+      <c r="H165" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Vendedor for 6/2026
  96
@@ -9158,39 +8951,39 @@
         </is>
       </c>
     </row>
-    <row r="170">
-      <c r="A170" s="2" t="inlineStr">
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C170" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D170" s="2" t="inlineStr">
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 20:23:50 +0000</t>
         </is>
       </c>
-      <c r="E170" s="2" t="inlineStr">
+      <c r="E166" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F170" s="2" t="inlineStr">
+      <c r="F166" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Factuur Fulfilled by Amazon for 6/2026</t>
         </is>
       </c>
-      <c r="G170" s="2" t="inlineStr"/>
-      <c r="H170" s="2" t="inlineStr">
+      <c r="G166" s="2" t="inlineStr"/>
+      <c r="H166" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Factuur Fulfilled by Amazon for 6/2026
  96
@@ -9214,39 +9007,39 @@
         </is>
       </c>
     </row>
-    <row r="171">
-      <c r="A171" s="2" t="inlineStr">
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B171" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C171" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D171" s="2" t="inlineStr">
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 20:07:18 +0000</t>
         </is>
       </c>
-      <c r="E171" s="2" t="inlineStr">
+      <c r="E167" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F171" s="2" t="inlineStr">
+      <c r="F167" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Faktura Säljare for 6/2026</t>
         </is>
       </c>
-      <c r="G171" s="2" t="inlineStr"/>
-      <c r="H171" s="2" t="inlineStr">
+      <c r="G167" s="2" t="inlineStr"/>
+      <c r="H167" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Faktura Säljare for 6/2026
  96
@@ -9273,39 +9066,39 @@
         </is>
       </c>
     </row>
-    <row r="172">
-      <c r="A172" s="2" t="inlineStr">
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B172" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C172" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D172" s="2" t="inlineStr">
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 20:02:23 +0000</t>
         </is>
       </c>
-      <c r="E172" s="2" t="inlineStr">
+      <c r="E168" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F172" s="2" t="inlineStr">
+      <c r="F168" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Faktura Fraktas Av Amazon for 6/2026</t>
         </is>
       </c>
-      <c r="G172" s="2" t="inlineStr"/>
-      <c r="H172" s="2" t="inlineStr">
+      <c r="G168" s="2" t="inlineStr"/>
+      <c r="H168" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Faktura Fraktas Av Amazon for 6/2026
  96
@@ -9332,39 +9125,39 @@
         </is>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" s="2" t="inlineStr">
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B173" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C173" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D173" s="2" t="inlineStr">
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 19:58:54 +0000</t>
         </is>
       </c>
-      <c r="E173" s="2" t="inlineStr">
+      <c r="E169" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F173" s="2" t="inlineStr">
+      <c r="F169" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Logística de Amazon for 6/2026</t>
         </is>
       </c>
-      <c r="G173" s="2" t="inlineStr"/>
-      <c r="H173" s="2" t="inlineStr">
+      <c r="G169" s="2" t="inlineStr"/>
+      <c r="H169" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Logística de Amazon for 6/2026
  96
@@ -9391,39 +9184,39 @@
         </is>
       </c>
     </row>
-    <row r="174">
-      <c r="A174" s="2" t="inlineStr">
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B174" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C174" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D174" s="2" t="inlineStr">
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 19:55:57 +0000</t>
         </is>
       </c>
-      <c r="E174" s="2" t="inlineStr">
+      <c r="E170" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F174" s="2" t="inlineStr">
+      <c r="F170" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Factuur Verkoper for 6/2026</t>
         </is>
       </c>
-      <c r="G174" s="2" t="inlineStr"/>
-      <c r="H174" s="2" t="inlineStr">
+      <c r="G170" s="2" t="inlineStr"/>
+      <c r="H170" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Factuur Verkoper for 6/2026
  96
@@ -9448,39 +9241,39 @@
         </is>
       </c>
     </row>
-    <row r="175">
-      <c r="A175" s="2" t="inlineStr">
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B175" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C175" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D175" s="2" t="inlineStr">
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 19:16:22 +0000</t>
         </is>
       </c>
-      <c r="E175" s="2" t="inlineStr">
+      <c r="E171" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F175" s="2" t="inlineStr">
+      <c r="F171" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Logística de Amazon for 6/2026</t>
         </is>
       </c>
-      <c r="G175" s="2" t="inlineStr"/>
-      <c r="H175" s="2" t="inlineStr">
+      <c r="G171" s="2" t="inlineStr"/>
+      <c r="H171" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Logística de Amazon for 6/2026
  96
@@ -9507,39 +9300,39 @@
         </is>
       </c>
     </row>
-    <row r="176">
-      <c r="A176" s="2" t="inlineStr">
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B176" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C176" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D176" s="2" t="inlineStr">
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 19:05:55 +0000</t>
         </is>
       </c>
-      <c r="E176" s="2" t="inlineStr">
+      <c r="E172" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F176" s="2" t="inlineStr">
+      <c r="F172" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.pl Faktura Sprzedawcy for 6/2026</t>
         </is>
       </c>
-      <c r="G176" s="2" t="inlineStr"/>
-      <c r="H176" s="2" t="inlineStr">
+      <c r="G172" s="2" t="inlineStr"/>
+      <c r="H172" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.pl Faktura Sprzedawcy for 6/2026
  96
@@ -9564,39 +9357,39 @@
         </is>
       </c>
     </row>
-    <row r="177">
-      <c r="A177" s="2" t="inlineStr">
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B177" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C177" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D177" s="2" t="inlineStr">
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 18:55:02 +0000</t>
         </is>
       </c>
-      <c r="E177" s="2" t="inlineStr">
+      <c r="E173" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F177" s="2" t="inlineStr">
+      <c r="F173" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 6/2026</t>
         </is>
       </c>
-      <c r="G177" s="2" t="inlineStr"/>
-      <c r="H177" s="2" t="inlineStr">
+      <c r="G173" s="2" t="inlineStr"/>
+      <c r="H173" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 6/2026
  96
@@ -9614,39 +9407,39 @@
         </is>
       </c>
     </row>
-    <row r="178">
-      <c r="A178" s="2" t="inlineStr">
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B178" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C178" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D178" s="2" t="inlineStr">
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 18:14:51 +0000</t>
         </is>
       </c>
-      <c r="E178" s="2" t="inlineStr">
+      <c r="E174" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F178" s="2" t="inlineStr">
+      <c r="F174" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Factuur Fulfilled by Amazon for 6/2026</t>
         </is>
       </c>
-      <c r="G178" s="2" t="inlineStr"/>
-      <c r="H178" s="2" t="inlineStr">
+      <c r="G174" s="2" t="inlineStr"/>
+      <c r="H174" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Factuur Fulfilled by Amazon for 6/2026
  96
@@ -9670,39 +9463,39 @@
         </is>
       </c>
     </row>
-    <row r="179">
-      <c r="A179" s="2" t="inlineStr">
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B179" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C179" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D179" s="2" t="inlineStr">
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 17:47:27 +0000</t>
         </is>
       </c>
-      <c r="E179" s="2" t="inlineStr">
+      <c r="E175" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F179" s="2" t="inlineStr">
+      <c r="F175" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Faktura Fraktas Av Amazon for 6/2026</t>
         </is>
       </c>
-      <c r="G179" s="2" t="inlineStr"/>
-      <c r="H179" s="2" t="inlineStr">
+      <c r="G175" s="2" t="inlineStr"/>
+      <c r="H175" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Faktura Fraktas Av Amazon for 6/2026
  96
@@ -9729,39 +9522,39 @@
         </is>
       </c>
     </row>
-    <row r="180">
-      <c r="A180" s="2" t="inlineStr">
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B180" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C180" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D180" s="2" t="inlineStr">
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 17:46:42 +0000</t>
         </is>
       </c>
-      <c r="E180" s="2" t="inlineStr">
+      <c r="E176" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F180" s="2" t="inlineStr">
+      <c r="F176" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ie Merchant Invoice for 6/2026</t>
         </is>
       </c>
-      <c r="G180" s="2" t="inlineStr"/>
-      <c r="H180" s="2" t="inlineStr">
+      <c r="G176" s="2" t="inlineStr"/>
+      <c r="H176" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ie Merchant Invoice for 6/2026
  96
@@ -9779,39 +9572,39 @@
         </is>
       </c>
     </row>
-    <row r="181">
-      <c r="A181" s="2" t="inlineStr">
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B181" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C181" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D181" s="2" t="inlineStr">
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 17:31:36 +0000</t>
         </is>
       </c>
-      <c r="E181" s="2" t="inlineStr">
+      <c r="E177" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F181" s="2" t="inlineStr">
+      <c r="F177" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 6/2026</t>
         </is>
       </c>
-      <c r="G181" s="2" t="inlineStr"/>
-      <c r="H181" s="2" t="inlineStr">
+      <c r="G177" s="2" t="inlineStr"/>
+      <c r="H177" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 6/2026
  96
@@ -9836,39 +9629,39 @@
         </is>
       </c>
     </row>
-    <row r="182">
-      <c r="A182" s="2" t="inlineStr">
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B182" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C182" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D182" s="2" t="inlineStr">
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 17:28:53 +0000</t>
         </is>
       </c>
-      <c r="E182" s="2" t="inlineStr">
+      <c r="E178" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F182" s="2" t="inlineStr">
+      <c r="F178" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ie Fulfillment by Amazon Merchant Invoice for 6/2026</t>
         </is>
       </c>
-      <c r="G182" s="2" t="inlineStr"/>
-      <c r="H182" s="2" t="inlineStr">
+      <c r="G178" s="2" t="inlineStr"/>
+      <c r="H178" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ie Fulfillment by Amazon Merchant Invoice for 6/2026
  96
@@ -9886,39 +9679,39 @@
         </is>
       </c>
     </row>
-    <row r="183">
-      <c r="A183" s="2" t="inlineStr">
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B183" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C183" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D183" s="2" t="inlineStr">
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 17:10:41 +0000</t>
         </is>
       </c>
-      <c r="E183" s="2" t="inlineStr">
+      <c r="E179" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F183" s="2" t="inlineStr">
+      <c r="F179" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Factuur Fulfilled by Amazon for 6/2026</t>
         </is>
       </c>
-      <c r="G183" s="2" t="inlineStr"/>
-      <c r="H183" s="2" t="inlineStr">
+      <c r="G179" s="2" t="inlineStr"/>
+      <c r="H179" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Factuur Fulfilled by Amazon for 6/2026
  96
@@ -9942,39 +9735,39 @@
         </is>
       </c>
     </row>
-    <row r="184">
-      <c r="A184" s="2" t="inlineStr">
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B184" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C184" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D184" s="2" t="inlineStr">
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 17:01:49 +0000</t>
         </is>
       </c>
-      <c r="E184" s="2" t="inlineStr">
+      <c r="E180" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F184" s="2" t="inlineStr">
+      <c r="F180" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ae Fulfillment by Amazon Merchant Invoice for 6/2026</t>
         </is>
       </c>
-      <c r="G184" s="2" t="inlineStr"/>
-      <c r="H184" s="2" t="inlineStr">
+      <c r="G180" s="2" t="inlineStr"/>
+      <c r="H180" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ae Fulfillment by Amazon Merchant Invoice for 6/2026
  96
@@ -9992,39 +9785,39 @@
         </is>
       </c>
     </row>
-    <row r="185">
-      <c r="A185" s="2" t="inlineStr">
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B185" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C185" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D185" s="2" t="inlineStr">
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 16:42:42 +0000</t>
         </is>
       </c>
-      <c r="E185" s="2" t="inlineStr">
+      <c r="E181" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F185" s="2" t="inlineStr">
+      <c r="F181" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk AGL Merchant Self-Billing Invoice for 6/2026</t>
         </is>
       </c>
-      <c r="G185" s="2" t="inlineStr"/>
-      <c r="H185" s="2" t="inlineStr">
+      <c r="G181" s="2" t="inlineStr"/>
+      <c r="H181" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk AGL Merchant Self-Billing Invoice for 6/2026
  96
@@ -10042,39 +9835,39 @@
         </is>
       </c>
     </row>
-    <row r="186">
-      <c r="A186" s="2" t="inlineStr">
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B186" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C186" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D186" s="2" t="inlineStr">
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 16:21:50 +0000</t>
         </is>
       </c>
-      <c r="E186" s="2" t="inlineStr">
+      <c r="E182" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F186" s="2" t="inlineStr">
+      <c r="F182" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Logística de Amazon for 6/2026</t>
         </is>
       </c>
-      <c r="G186" s="2" t="inlineStr"/>
-      <c r="H186" s="2" t="inlineStr">
+      <c r="G182" s="2" t="inlineStr"/>
+      <c r="H182" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Logística de Amazon for 6/2026
  96
@@ -10101,39 +9894,39 @@
         </is>
       </c>
     </row>
-    <row r="187">
-      <c r="A187" s="2" t="inlineStr">
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B187" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C187" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D187" s="2" t="inlineStr">
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 16:02:53 +0000</t>
         </is>
       </c>
-      <c r="E187" s="2" t="inlineStr">
+      <c r="E183" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F187" s="2" t="inlineStr">
+      <c r="F183" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 6/2026</t>
         </is>
       </c>
-      <c r="G187" s="2" t="inlineStr"/>
-      <c r="H187" s="2" t="inlineStr">
+      <c r="G183" s="2" t="inlineStr"/>
+      <c r="H183" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 6/2026
  96
@@ -10158,40 +9951,40 @@
         </is>
       </c>
     </row>
-    <row r="188">
-      <c r="A188" s="2" t="inlineStr">
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B188" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C188" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D188" s="2" t="inlineStr">
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 15:46:03 +0000</t>
         </is>
       </c>
-      <c r="E188" s="2" t="inlineStr">
+      <c r="E184" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F188" s="2" t="inlineStr">
+      <c r="F184" s="2" t="inlineStr">
         <is>
           <t>Your VAT invoice for EPR Pay on Behalf charges for Amazon.co.uk
  sales</t>
         </is>
       </c>
-      <c r="G188" s="2" t="inlineStr"/>
-      <c r="H188" s="2" t="inlineStr">
+      <c r="G184" s="2" t="inlineStr"/>
+      <c r="H184" s="2" t="inlineStr">
         <is>
           <t>Your VAT invoice for EPR Pay on Behalf charges for Amazon.co.uk sales
  96
@@ -10206,39 +9999,39 @@
         </is>
       </c>
     </row>
-    <row r="189">
-      <c r="A189" s="2" t="inlineStr">
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B189" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C189" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D189" s="2" t="inlineStr">
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 15:40:18 +0000</t>
         </is>
       </c>
-      <c r="E189" s="2" t="inlineStr">
+      <c r="E185" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F189" s="2" t="inlineStr">
+      <c r="F185" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com.be Factuur Verkoper for 6/2026</t>
         </is>
       </c>
-      <c r="G189" s="2" t="inlineStr"/>
-      <c r="H189" s="2" t="inlineStr">
+      <c r="G185" s="2" t="inlineStr"/>
+      <c r="H185" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com.be Factuur Verkoper for 6/2026
  96
@@ -10259,39 +10052,39 @@
         </is>
       </c>
     </row>
-    <row r="190">
-      <c r="A190" s="2" t="inlineStr">
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B190" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C190" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D190" s="2" t="inlineStr">
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 15:35:08 +0000</t>
         </is>
       </c>
-      <c r="E190" s="2" t="inlineStr">
+      <c r="E186" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F190" s="2" t="inlineStr">
+      <c r="F186" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Factuur Fulfilled by Amazon for 6/2026</t>
         </is>
       </c>
-      <c r="G190" s="2" t="inlineStr"/>
-      <c r="H190" s="2" t="inlineStr">
+      <c r="G186" s="2" t="inlineStr"/>
+      <c r="H186" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Factuur Fulfilled by Amazon for 6/2026
  96
@@ -10315,39 +10108,39 @@
         </is>
       </c>
     </row>
-    <row r="191">
-      <c r="A191" s="2" t="inlineStr">
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B191" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C191" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D191" s="2" t="inlineStr">
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 15:30:53 +0000</t>
         </is>
       </c>
-      <c r="E191" s="2" t="inlineStr">
+      <c r="E187" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F191" s="2" t="inlineStr">
+      <c r="F187" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 6/2026</t>
         </is>
       </c>
-      <c r="G191" s="2" t="inlineStr"/>
-      <c r="H191" s="2" t="inlineStr">
+      <c r="G187" s="2" t="inlineStr"/>
+      <c r="H187" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 6/2026
  96
@@ -10365,39 +10158,39 @@
         </is>
       </c>
     </row>
-    <row r="192">
-      <c r="A192" s="2" t="inlineStr">
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B192" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C192" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D192" s="2" t="inlineStr">
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 14:51:08 +0000</t>
         </is>
       </c>
-      <c r="E192" s="2" t="inlineStr">
+      <c r="E188" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F192" s="2" t="inlineStr">
+      <c r="F188" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ae Merchant Invoice for 6/2026</t>
         </is>
       </c>
-      <c r="G192" s="2" t="inlineStr"/>
-      <c r="H192" s="2" t="inlineStr">
+      <c r="G188" s="2" t="inlineStr"/>
+      <c r="H188" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ae Merchant Invoice for 6/2026
  96
@@ -10420,39 +10213,39 @@
         </is>
       </c>
     </row>
-    <row r="193">
-      <c r="A193" s="2" t="inlineStr">
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B193" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C193" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D193" s="2" t="inlineStr">
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="inlineStr">
         <is>
           <t>Sun, 5 Jul 2026 13:53:08 +0000</t>
         </is>
       </c>
-      <c r="E193" s="2" t="inlineStr">
+      <c r="E189" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F193" s="2" t="inlineStr">
+      <c r="F189" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G193" s="2" t="inlineStr"/>
-      <c r="H193" s="2" t="inlineStr">
+      <c r="G189" s="2" t="inlineStr"/>
+      <c r="H189" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -10467,39 +10260,39 @@
         </is>
       </c>
     </row>
-    <row r="194">
-      <c r="A194" s="2" t="inlineStr">
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B194" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C194" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D194" s="2" t="inlineStr">
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
         <is>
           <t>Sun, 5 Jul 2026 12:49:39 +0000</t>
         </is>
       </c>
-      <c r="E194" s="2" t="inlineStr">
+      <c r="E190" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F194" s="2" t="inlineStr">
+      <c r="F190" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G194" s="2" t="inlineStr"/>
-      <c r="H194" s="2" t="inlineStr">
+      <c r="G190" s="2" t="inlineStr"/>
+      <c r="H190" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -10514,39 +10307,39 @@
         </is>
       </c>
     </row>
-    <row r="195">
-      <c r="A195" s="2" t="inlineStr">
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B195" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C195" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D195" s="2" t="inlineStr">
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Jul 2026 14:26:45 +0000</t>
         </is>
       </c>
-      <c r="E195" s="2" t="inlineStr">
+      <c r="E191" s="2" t="inlineStr">
         <is>
           <t>Amazon Services Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F195" s="2" t="inlineStr">
+      <c r="F191" s="2" t="inlineStr">
         <is>
           <t>El Asistente de vendedores ya está activo en Francia, Italia y España</t>
         </is>
       </c>
-      <c r="G195" s="2" t="inlineStr"/>
-      <c r="H195" s="2" t="inlineStr">
+      <c r="G191" s="2" t="inlineStr"/>
+      <c r="H191" s="2" t="inlineStr">
         <is>
           <t>96
  La asistencia con tecnología de IA ya está disponible en Seller Central para ayudarte a gestionar tu negocio de forma más eficiente.
@@ -10560,39 +10353,39 @@
         </is>
       </c>
     </row>
-    <row r="196">
-      <c r="A196" s="2" t="inlineStr">
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B196" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C196" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D196" s="2" t="inlineStr">
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Jul 2026 14:11:01 +0000</t>
         </is>
       </c>
-      <c r="E196" s="2" t="inlineStr">
+      <c r="E192" s="2" t="inlineStr">
         <is>
           <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F196" s="2" t="inlineStr">
+      <c r="F192" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G196" s="2" t="inlineStr"/>
-      <c r="H196" s="2" t="inlineStr">
+      <c r="G192" s="2" t="inlineStr"/>
+      <c r="H192" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Luana Camargo, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -10610,39 +10403,39 @@
         </is>
       </c>
     </row>
-    <row r="197">
-      <c r="A197" s="2" t="inlineStr">
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B197" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C197" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D197" s="2" t="inlineStr">
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Jul 2026 13:49:18 +0000</t>
         </is>
       </c>
-      <c r="E197" s="2" t="inlineStr">
+      <c r="E193" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F197" s="2" t="inlineStr">
+      <c r="F193" s="2" t="inlineStr">
         <is>
           <t>L'assistente venditori è ora attivo in Francia, Italia e Spagna</t>
         </is>
       </c>
-      <c r="G197" s="2" t="inlineStr"/>
-      <c r="H197" s="2" t="inlineStr">
+      <c r="G193" s="2" t="inlineStr"/>
+      <c r="H193" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  L'assistenza basata su AI è ora disponibile in Seller Central per aiutarti a gestire la tua attività in modo più efficiente.
@@ -10657,39 +10450,39 @@
         </is>
       </c>
     </row>
-    <row r="198">
-      <c r="A198" s="2" t="inlineStr">
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B198" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C198" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D198" s="2" t="inlineStr">
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Jul 2026 16:04:35 +0000</t>
         </is>
       </c>
-      <c r="E198" s="2" t="inlineStr">
+      <c r="E194" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F198" s="2" t="inlineStr">
+      <c r="F194" s="2" t="inlineStr">
         <is>
           <t>Presentar información de cumplimiento normativo de la RAP en Portugal</t>
         </is>
       </c>
-      <c r="G198" s="2" t="inlineStr"/>
-      <c r="H198" s="2" t="inlineStr">
+      <c r="G194" s="2" t="inlineStr"/>
+      <c r="H194" s="2" t="inlineStr">
         <is>
           <t>96
  La normativa portuguesa sobre la RAP se aplica a los productos vendidos a clientes de Portugal.
@@ -10706,39 +10499,39 @@
         </is>
       </c>
     </row>
-    <row r="199">
-      <c r="A199" s="2" t="inlineStr">
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B199" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C199" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D199" s="2" t="inlineStr">
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Jul 2026 02:53:05 +0000</t>
         </is>
       </c>
-      <c r="E199" s="2" t="inlineStr">
+      <c r="E195" s="2" t="inlineStr">
         <is>
           <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F199" s="2" t="inlineStr">
+      <c r="F195" s="2" t="inlineStr">
         <is>
           <t>Transparency Invoice/Credit note for 06/2026</t>
         </is>
       </c>
-      <c r="G199" s="2" t="inlineStr"/>
-      <c r="H199" s="2" t="inlineStr">
+      <c r="G195" s="2" t="inlineStr"/>
+      <c r="H195" s="2" t="inlineStr">
         <is>
           <t>96
  Dear Customer,
@@ -10756,39 +10549,39 @@
         </is>
       </c>
     </row>
-    <row r="200">
-      <c r="A200" s="2" t="inlineStr">
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B200" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C200" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D200" s="2" t="inlineStr">
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
         <is>
           <t>Tue, 30 Jun 2026 00:26:34 +0000</t>
         </is>
       </c>
-      <c r="E200" s="2" t="inlineStr">
+      <c r="E196" s="2" t="inlineStr">
         <is>
           <t>Assistenza venditori Amazon &lt;merch.service05@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F200" s="2" t="inlineStr">
+      <c r="F196" s="2" t="inlineStr">
         <is>
           <t>&lt;p&gt;Grazie per aver creato un nuovo caso: -- 12929127032&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="G200" s="2" t="inlineStr"/>
-      <c r="H200" s="2" t="inlineStr">
+      <c r="G196" s="2" t="inlineStr"/>
+      <c r="H196" s="2" t="inlineStr">
         <is>
           <t>96
 &lt;p&gt;Grazie per aver creato un nuovo caso: -- 12929127032&lt;/p&gt;
@@ -10803,39 +10596,39 @@
         </is>
       </c>
     </row>
-    <row r="201">
-      <c r="A201" s="2" t="inlineStr">
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B201" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C201" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D201" s="2" t="inlineStr">
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="inlineStr">
         <is>
           <t>Mon, 29 Jun 2026 14:10:24 +0000</t>
         </is>
       </c>
-      <c r="E201" s="2" t="inlineStr">
+      <c r="E197" s="2" t="inlineStr">
         <is>
           <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F201" s="2" t="inlineStr">
+      <c r="F197" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G201" s="2" t="inlineStr"/>
-      <c r="H201" s="2" t="inlineStr">
+      <c r="G197" s="2" t="inlineStr"/>
+      <c r="H197" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -10851,39 +10644,39 @@
         </is>
       </c>
     </row>
-    <row r="202">
-      <c r="A202" s="2" t="inlineStr">
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B202" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C202" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D202" s="2" t="inlineStr">
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
         <is>
           <t>Fri, 26 Jun 2026 14:40:10 +0000</t>
         </is>
       </c>
-      <c r="E202" s="2" t="inlineStr">
+      <c r="E198" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F202" s="2" t="inlineStr">
+      <c r="F198" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G202" s="2" t="inlineStr"/>
-      <c r="H202" s="2" t="inlineStr">
+      <c r="G198" s="2" t="inlineStr"/>
+      <c r="H198" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -10898,39 +10691,39 @@
         </is>
       </c>
     </row>
-    <row r="203">
-      <c r="A203" s="2" t="inlineStr">
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B203" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C203" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D203" s="2" t="inlineStr">
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
         <is>
           <t>Fri, 26 Jun 2026 14:07:09 +0000</t>
         </is>
       </c>
-      <c r="E203" s="2" t="inlineStr">
+      <c r="E199" s="2" t="inlineStr">
         <is>
           <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F203" s="2" t="inlineStr">
+      <c r="F199" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G203" s="2" t="inlineStr"/>
-      <c r="H203" s="2" t="inlineStr">
+      <c r="G199" s="2" t="inlineStr"/>
+      <c r="H199" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Luana Camargo, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -10958,39 +10751,39 @@
         </is>
       </c>
     </row>
-    <row r="204">
-      <c r="A204" s="2" t="inlineStr">
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B204" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C204" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D204" s="2" t="inlineStr">
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
         <is>
           <t>Thu, 25 Jun 2026 22:31:41 +0000</t>
         </is>
       </c>
-      <c r="E204" s="2" t="inlineStr">
+      <c r="E200" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon &lt;no-reply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F204" s="2" t="inlineStr">
+      <c r="F200" s="2" t="inlineStr">
         <is>
           <t>Tus límites de capacidad de Logística de Amazon para julio</t>
         </is>
       </c>
-      <c r="G204" s="2" t="inlineStr"/>
-      <c r="H204" s="2" t="inlineStr">
+      <c r="G200" s="2" t="inlineStr"/>
+      <c r="H200" s="2" t="inlineStr">
         <is>
           <t>96
  Tus límites de capacidad de Logística de Amazon para julio
@@ -11019,39 +10812,39 @@
         </is>
       </c>
     </row>
-    <row r="205">
-      <c r="A205" s="2" t="inlineStr">
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B205" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C205" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D205" s="2" t="inlineStr">
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="inlineStr">
         <is>
           <t>Thu, 25 Jun 2026 01:48:42 +0000</t>
         </is>
       </c>
-      <c r="E205" s="2" t="inlineStr">
+      <c r="E201" s="2" t="inlineStr">
         <is>
           <t>Zespół Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F205" s="2" t="inlineStr">
+      <c r="F201" s="2" t="inlineStr">
         <is>
           <t>Łącze do zaktualizowanego raportu podatkowego dotyczącego Chin za okres od października do grudnia 2025 r.</t>
         </is>
       </c>
-      <c r="G205" s="2" t="inlineStr"/>
-      <c r="H205" s="2" t="inlineStr">
+      <c r="G201" s="2" t="inlineStr"/>
+      <c r="H201" s="2" t="inlineStr">
         <is>
           <t>96
  Ponownie przesyłamy kwartalny raport podatkowy, który obejmuje dane takie jak informacje o tożsamości, liczba transakcji, przychody oraz prowizje i opłaty za usługi.
@@ -11069,39 +10862,39 @@
         </is>
       </c>
     </row>
-    <row r="206">
-      <c r="A206" s="2" t="inlineStr">
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B206" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C206" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D206" s="2" t="inlineStr">
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr">
         <is>
           <t>Wed, 24 Jun 2026 10:01:00 +0000</t>
         </is>
       </c>
-      <c r="E206" s="2" t="inlineStr">
+      <c r="E202" s="2" t="inlineStr">
         <is>
           <t>The Fulfillment by Amazon team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F206" s="2" t="inlineStr">
+      <c r="F202" s="2" t="inlineStr">
         <is>
           <t>Act today &amp; improve Sales on Excess Inventory</t>
         </is>
       </c>
-      <c r="G206" s="2" t="inlineStr"/>
-      <c r="H206" s="2" t="inlineStr">
+      <c r="G202" s="2" t="inlineStr"/>
+      <c r="H202" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -11120,39 +10913,39 @@
         </is>
       </c>
     </row>
-    <row r="207">
-      <c r="A207" s="2" t="inlineStr">
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B207" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C207" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D207" s="2" t="inlineStr">
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="inlineStr">
         <is>
           <t>Tue, 23 Jun 2026 16:59:26 +0000</t>
         </is>
       </c>
-      <c r="E207" s="2" t="inlineStr">
+      <c r="E203" s="2" t="inlineStr">
         <is>
           <t>Zespół Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F207" s="2" t="inlineStr">
+      <c r="F203" s="2" t="inlineStr">
         <is>
           <t>Pobierz raport podatkowy dla Chin za okres od października do grudnia 2025 r.</t>
         </is>
       </c>
-      <c r="G207" s="2" t="inlineStr"/>
-      <c r="H207" s="2" t="inlineStr">
+      <c r="G203" s="2" t="inlineStr"/>
+      <c r="H203" s="2" t="inlineStr">
         <is>
           <t>96
  Możesz teraz pobrać kwartalny raport podatkowy, który zawiera dane, takie jak informacje identyfikacyjne, liczba transakcji, przychody oraz prowizje i opłaty za usługi.
@@ -11166,39 +10959,39 @@
         </is>
       </c>
     </row>
-    <row r="208">
-      <c r="A208" s="2" t="inlineStr">
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B208" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C208" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D208" s="2" t="inlineStr">
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
         <is>
           <t>Tue, 23 Jun 2026 00:26:49 +0000</t>
         </is>
       </c>
-      <c r="E208" s="2" t="inlineStr">
+      <c r="E204" s="2" t="inlineStr">
         <is>
           <t>Assistenza venditori Amazon &lt;merch.service05@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F208" s="2" t="inlineStr">
+      <c r="F204" s="2" t="inlineStr">
         <is>
           <t>&lt;p&gt;Grazie per aver creato un nuovo caso: -- 12908112692&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="G208" s="2" t="inlineStr"/>
-      <c r="H208" s="2" t="inlineStr">
+      <c r="G204" s="2" t="inlineStr"/>
+      <c r="H204" s="2" t="inlineStr">
         <is>
           <t>96
 &lt;p&gt;Grazie per aver creato un nuovo caso: -- 12908112692&lt;/p&gt;
@@ -11213,39 +11006,39 @@
         </is>
       </c>
     </row>
-    <row r="209">
-      <c r="A209" s="2" t="inlineStr">
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B209" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C209" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D209" s="2" t="inlineStr">
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C205" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D205" s="2" t="inlineStr">
         <is>
           <t>Mon, 22 Jun 2026 09:29:52 +0000</t>
         </is>
       </c>
-      <c r="E209" s="2" t="inlineStr">
+      <c r="E205" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F209" s="2" t="inlineStr">
+      <c r="F205" s="2" t="inlineStr">
         <is>
           <t>Prime会员日明天开始：最后提报促销活动的机会</t>
         </is>
       </c>
-      <c r="G209" s="2" t="inlineStr"/>
-      <c r="H209" s="2" t="inlineStr">
+      <c r="G205" s="2" t="inlineStr"/>
+      <c r="H205" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Prime Day 业绩
 尊敬的卖家，
@@ -11269,39 +11062,39 @@
         </is>
       </c>
     </row>
-    <row r="210">
-      <c r="A210" s="2" t="inlineStr">
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B210" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C210" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D210" s="2" t="inlineStr">
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="inlineStr">
         <is>
           <t>Sun, 21 Jun 2026 12:49:43 +0000</t>
         </is>
       </c>
-      <c r="E210" s="2" t="inlineStr">
+      <c r="E206" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F210" s="2" t="inlineStr">
+      <c r="F206" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G210" s="2" t="inlineStr"/>
-      <c r="H210" s="2" t="inlineStr">
+      <c r="G206" s="2" t="inlineStr"/>
+      <c r="H206" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -11316,92 +11109,39 @@
         </is>
       </c>
     </row>
-    <row r="211">
-      <c r="A211" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B211" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C211" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D211" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 20 Jun 2026 10:18:43 +0000</t>
-        </is>
-      </c>
-      <c r="E211" s="2" t="inlineStr">
-        <is>
-          <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
-        </is>
-      </c>
-      <c r="F211" s="2" t="inlineStr">
-        <is>
-          <t>Dein Einkaufswagen wartet</t>
-        </is>
-      </c>
-      <c r="G211" s="2" t="inlineStr"/>
-      <c r="H211" s="2" t="inlineStr">
-        <is>
-          <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
-Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
- -3 % 27,95 € UVP: 28,95 €
-https://www.amazon.de/gp/product/B0DRCF83VZ/?ref_=
-Einkaufswagen anzeigen
-https://www.amazon.de/gp/cart/view.html?ref_=cor
-Schaue dir weitere Optionen an
-75x120 cm Feuerfeste Unterlage, Hitzeschutzmatte, Antihaft-Material Bodenschutzmatte, Grill Matten, Bodenmatte Feuerstellenmatte Outdoor BBQ Matte für Gasgrill Holzkohlegrill
- 19,99 €
-https://www.amazon.de/gp/product/B0DBLM41YS/?ref_=ci_mcx_mr_2p_0_lm
-Feuerfeste Unterlage, 130 × 80cm Hitzebeständig bis 982 ℃ Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Grill Matte für Gasgrill Holzkohlegrill
- -8 % 23,95 € UVP: 25,95 €
-https://www.amazon.de/gp/product/B0DRC8LPGS/?ref_=ci_mcx_mr_2p_1_lm
-Alckijy Feuerfeste Unterlage | 100 * 150cm Faltbare Hitzeschutzmatte | Bodenschutzmatte | Grillmatten | Bodenmatte | Grillteppich | Funkenschutzplatte | für BBQ Grills Kaminöfen Boden Rasen usw
-Befristetes Angebot -18 % 20,38 € UVP: 24,95 €
-h</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" s="2" t="inlineStr">
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B212" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C212" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D212" s="2" t="inlineStr">
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C207" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D207" s="2" t="inlineStr">
         <is>
           <t>Sat, 11 Jul 2026 04:26:29 +0000</t>
         </is>
       </c>
-      <c r="E212" s="2" t="inlineStr">
+      <c r="E207" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F212" s="2" t="inlineStr">
+      <c r="F207" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-07-23</t>
         </is>
       </c>
-      <c r="G212" s="2" t="inlineStr"/>
-      <c r="H212" s="2" t="inlineStr">
+      <c r="G207" s="2" t="inlineStr"/>
+      <c r="H207" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -11422,39 +11162,39 @@
         </is>
       </c>
     </row>
-    <row r="213">
-      <c r="A213" s="2" t="inlineStr">
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B213" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C213" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D213" s="2" t="inlineStr">
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D208" s="2" t="inlineStr">
         <is>
           <t>Sat, 11 Jul 2026 04:08:56 +0000</t>
         </is>
       </c>
-      <c r="E213" s="2" t="inlineStr">
+      <c r="E208" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F213" s="2" t="inlineStr">
+      <c r="F208" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G213" s="2" t="inlineStr"/>
-      <c r="H213" s="2" t="inlineStr">
+      <c r="G208" s="2" t="inlineStr"/>
+      <c r="H208" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -11477,39 +11217,39 @@
         </is>
       </c>
     </row>
-    <row r="214">
-      <c r="A214" s="2" t="inlineStr">
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B214" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C214" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D214" s="2" t="inlineStr">
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C209" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D209" s="2" t="inlineStr">
         <is>
           <t>Sat, 11 Jul 2026 03:06:39 +0000</t>
         </is>
       </c>
-      <c r="E214" s="2" t="inlineStr">
+      <c r="E209" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F214" s="2" t="inlineStr">
+      <c r="F209" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-07-23</t>
         </is>
       </c>
-      <c r="G214" s="2" t="inlineStr"/>
-      <c r="H214" s="2" t="inlineStr">
+      <c r="G209" s="2" t="inlineStr"/>
+      <c r="H209" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -11532,39 +11272,39 @@
         </is>
       </c>
     </row>
-    <row r="215">
-      <c r="A215" s="2" t="inlineStr">
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B215" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C215" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D215" s="2" t="inlineStr">
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D210" s="2" t="inlineStr">
         <is>
           <t>Sat, 4 Jul 2026 04:34:30 +0000</t>
         </is>
       </c>
-      <c r="E215" s="2" t="inlineStr">
+      <c r="E210" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F215" s="2" t="inlineStr">
+      <c r="F210" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G215" s="2" t="inlineStr"/>
-      <c r="H215" s="2" t="inlineStr">
+      <c r="G210" s="2" t="inlineStr"/>
+      <c r="H210" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -11588,39 +11328,39 @@
         </is>
       </c>
     </row>
-    <row r="216">
-      <c r="A216" s="2" t="inlineStr">
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B216" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C216" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D216" s="2" t="inlineStr">
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C211" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D211" s="2" t="inlineStr">
         <is>
           <t>Sat, 4 Jul 2026 03:35:02 +0000</t>
         </is>
       </c>
-      <c r="E216" s="2" t="inlineStr">
+      <c r="E211" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F216" s="2" t="inlineStr">
+      <c r="F211" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-07-16</t>
         </is>
       </c>
-      <c r="G216" s="2" t="inlineStr"/>
-      <c r="H216" s="2" t="inlineStr">
+      <c r="G211" s="2" t="inlineStr"/>
+      <c r="H211" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -11643,39 +11383,39 @@
         </is>
       </c>
     </row>
-    <row r="217">
-      <c r="A217" s="2" t="inlineStr">
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B217" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C217" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D217" s="2" t="inlineStr">
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D212" s="2" t="inlineStr">
         <is>
           <t>Sat, 4 Jul 2026 03:23:13 +0000</t>
         </is>
       </c>
-      <c r="E217" s="2" t="inlineStr">
+      <c r="E212" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F217" s="2" t="inlineStr">
+      <c r="F212" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-07-16</t>
         </is>
       </c>
-      <c r="G217" s="2" t="inlineStr"/>
-      <c r="H217" s="2" t="inlineStr">
+      <c r="G212" s="2" t="inlineStr"/>
+      <c r="H212" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -11696,39 +11436,39 @@
         </is>
       </c>
     </row>
-    <row r="218">
-      <c r="A218" s="2" t="inlineStr">
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B218" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C218" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D218" s="2" t="inlineStr">
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C213" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D213" s="2" t="inlineStr">
         <is>
           <t>Sat, 27 Jun 2026 04:46:44 +0000</t>
         </is>
       </c>
-      <c r="E218" s="2" t="inlineStr">
+      <c r="E213" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F218" s="2" t="inlineStr">
+      <c r="F213" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G218" s="2" t="inlineStr"/>
-      <c r="H218" s="2" t="inlineStr">
+      <c r="G213" s="2" t="inlineStr"/>
+      <c r="H213" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -11752,39 +11492,39 @@
         </is>
       </c>
     </row>
-    <row r="219">
-      <c r="A219" s="2" t="inlineStr">
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B219" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C219" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D219" s="2" t="inlineStr">
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D214" s="2" t="inlineStr">
         <is>
           <t>Sat, 27 Jun 2026 04:45:39 +0000</t>
         </is>
       </c>
-      <c r="E219" s="2" t="inlineStr">
+      <c r="E214" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F219" s="2" t="inlineStr">
+      <c r="F214" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G219" s="2" t="inlineStr"/>
-      <c r="H219" s="2" t="inlineStr">
+      <c r="G214" s="2" t="inlineStr"/>
+      <c r="H214" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -11808,39 +11548,39 @@
         </is>
       </c>
     </row>
-    <row r="220">
-      <c r="A220" s="2" t="inlineStr">
+    <row r="215">
+      <c r="A215" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B220" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C220" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D220" s="2" t="inlineStr">
+      <c r="B215" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C215" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D215" s="2" t="inlineStr">
         <is>
           <t>Sat, 27 Jun 2026 03:25:54 +0000</t>
         </is>
       </c>
-      <c r="E220" s="2" t="inlineStr">
+      <c r="E215" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F220" s="2" t="inlineStr">
+      <c r="F215" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-07-09</t>
         </is>
       </c>
-      <c r="G220" s="2" t="inlineStr"/>
-      <c r="H220" s="2" t="inlineStr">
+      <c r="G215" s="2" t="inlineStr"/>
+      <c r="H215" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -11862,150 +11602,40 @@
         </is>
       </c>
     </row>
-    <row r="221">
-      <c r="A221" s="2" t="inlineStr">
-        <is>
-          <t>货件/库存类</t>
-        </is>
-      </c>
-      <c r="B221" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C221" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D221" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 20 Jun 2026 04:59:29 +0000</t>
-        </is>
-      </c>
-      <c r="E221" s="2" t="inlineStr">
-        <is>
-          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F221" s="2" t="inlineStr">
-        <is>
-          <t>Disposal order created for unsellable FBA inventory</t>
-        </is>
-      </c>
-      <c r="G221" s="2" t="inlineStr"/>
-      <c r="H221" s="2" t="inlineStr">
-        <is>
-          <t>96
-Automated Removals of Unfulfillable Inventory
- Final notice: Disposal order for your unfulfillable FBA inventory
- Final notice: Disposal order for your unfulfillable FBA inventory
- Hello,
-You have unfulfillable inventory that has been in a fulfilment centre for more than 14 days. We have created a disposal order for these items.
- Why is this happening?
-This action is required because these unfulfillable items have remained in our fulfilment centres for more than 14 days after notification. According to our FBA Required Removals policy, cancelling a required removal order is not permitted. To learn more, visit our FBA Required Removals policy .
- Removal order ID:
-- 9U/Ti42WHq
- Unsellable Products:
-- FNSKU: B0DRC8LPGS Quantity: 1
-- FNSKU: X002A05YW5 Quantity: 1
- For more information about the disposal order process, see Remove inventory from a fulfilment centre .
- To monitor your unfulfillable inventory, see the Manage FBA Inventory for total unsellable quantities or the Recommended Removal report for unsellable and aged inventory details.
- The Fulfilment by Amazon Team
- Report an issue with this email
- If you have any questions visit: Seller Central
- To change your email preferen</t>
-        </is>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" s="2" t="inlineStr">
-        <is>
-          <t>货件/库存类</t>
-        </is>
-      </c>
-      <c r="B222" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C222" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D222" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 20 Jun 2026 03:24:34 +0000</t>
-        </is>
-      </c>
-      <c r="E222" s="2" t="inlineStr">
-        <is>
-          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F222" s="2" t="inlineStr">
-        <is>
-          <t>Create FBA removal order by 2026-07-02</t>
-        </is>
-      </c>
-      <c r="G222" s="2" t="inlineStr"/>
-      <c r="H222" s="2" t="inlineStr">
-        <is>
-          <t>96
-Automated removals of unfulfillable inventory
- Required removals: First notification
- Required removals: First notification
- Hello,
-Your FBA inventory listed below became unsellable in the past seven days. You must create a removal order by 2026-07-02 or these items will be disposed of. Removal fees will apply. Review the affected items and next steps below.
-Unsellable products:
-- FNSKU: B0DRCB74YN Quantity: 3
-- FNSKU: B0DRCF83VZ Quantity: 2
- Why is this happening?
-This action is required because these items are no longer in sellable condition in our fulfilment centres. According to our FBA Required Removals policy, all unsuitable units must be removed within 14 days of notification. To learn more, go to our FBA Required Removals policy .
-We leveraged a combination of automated means to identify this issue and make this decision.
- How do I address this?
-Follow these steps to manage your unsellable inventory:
-- Check your complete list and quantity of unsellable items in the Manage FBA inventory .
-- Create a removal order (removal fees apply) by following the instructions in Remove inventory overview .
- To avoid future manual inventory removal orders, set up Automated Unfulfillab</t>
-        </is>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" s="2" t="inlineStr">
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B223" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C223" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D223" s="2" t="inlineStr">
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C216" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D216" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 03:21:27 +0000</t>
         </is>
       </c>
-      <c r="E223" s="2" t="inlineStr">
+      <c r="E216" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central Communications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F223" s="2" t="inlineStr">
+      <c r="F216" s="2" t="inlineStr">
         <is>
           <t>[Amazon.co.uk] One or More of Your Amazon Listings Have Been Search
  Suppressed</t>
         </is>
       </c>
-      <c r="G223" s="2" t="inlineStr"/>
-      <c r="H223" s="2" t="inlineStr">
+      <c r="G216" s="2" t="inlineStr"/>
+      <c r="H216" s="2" t="inlineStr">
         <is>
           <t>96
 [Amazon.co.uk] One or More of Your Amazon Listings Have Been Search Suppressed
@@ -12022,39 +11652,39 @@
         </is>
       </c>
     </row>
-    <row r="224">
-      <c r="A224" s="2" t="inlineStr">
+    <row r="217">
+      <c r="A217" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B224" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C224" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D224" s="2" t="inlineStr">
+      <c r="B217" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C217" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D217" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Jul 2026 00:16:50 +0000</t>
         </is>
       </c>
-      <c r="E224" s="2" t="inlineStr">
+      <c r="E217" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F224" s="2" t="inlineStr">
+      <c r="F217" s="2" t="inlineStr">
         <is>
           <t>View your US Q3-2026 CSBA fee rate</t>
         </is>
       </c>
-      <c r="G224" s="2" t="inlineStr"/>
-      <c r="H224" s="2" t="inlineStr">
+      <c r="G217" s="2" t="inlineStr"/>
+      <c r="H217" s="2" t="inlineStr">
         <is>
           <t>96
  (Important) CSBA US Fee rate for Q3-2026
@@ -12084,39 +11714,39 @@
         </is>
       </c>
     </row>
-    <row r="225">
-      <c r="A225" s="2" t="inlineStr">
+    <row r="218">
+      <c r="A218" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B225" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C225" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D225" s="2" t="inlineStr">
+      <c r="B218" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C218" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D218" s="2" t="inlineStr">
         <is>
           <t>Thu, 25 Jun 2026 12:14:25 +0000</t>
         </is>
       </c>
-      <c r="E225" s="2" t="inlineStr">
+      <c r="E218" s="2" t="inlineStr">
         <is>
           <t>Sell with Amazon &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F225" s="2" t="inlineStr">
+      <c r="F218" s="2" t="inlineStr">
         <is>
           <t>Connect with an Amazon expert at Seller Café—Save $100 with early-bird pricing</t>
         </is>
       </c>
-      <c r="G225" s="2" t="inlineStr"/>
-      <c r="H225" s="2" t="inlineStr">
+      <c r="G218" s="2" t="inlineStr"/>
+      <c r="H218" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/-ld-EM/7z46y96/6733799304/h/qLPgz01lmZlp6bu7C295K13RXyMwFkd7KKOkI6IliSc)
 [Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/4uHYwMZ-ld-EM/7z46y99/6733799304/h/qLPgz01lmZlp6bu7C295K13RXyMwFkd7KKOkI6IliSc)
